--- a/data-processed/summary_stats.xlsx
+++ b/data-processed/summary_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bbf9a23e224bd51a/Documents/GitHub/Chlamy_37_pops_pheno_constraint/data-processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{7541FEAE-B6A3-48A6-8A9B-D64358009044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB48A33-7770-4910-9CDD-31FF4AB7C633}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{7541FEAE-B6A3-48A6-8A9B-D64358009044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C682A379-637F-4802-8AAA-5F43A2071EB7}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FF39BB7-E2B9-45F5-8657-83F250E9A4B6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="49">
   <si>
     <t>Gradients</t>
   </si>
@@ -120,6 +120,69 @@
   </si>
   <si>
     <t>`-1.66817, p 0.04733</t>
+  </si>
+  <si>
+    <t>`0.03581, p 0.05961</t>
+  </si>
+  <si>
+    <t>`0.08403, p 0.14458</t>
+  </si>
+  <si>
+    <t>`0.18766, p 0.10838</t>
+  </si>
+  <si>
+    <t>`0.00558, p 0.12478</t>
+  </si>
+  <si>
+    <t>`0.00226, p 0.51784</t>
+  </si>
+  <si>
+    <t>`-0.00530, p 0.38206</t>
+  </si>
+  <si>
+    <t>`0.00144, p 0.59239</t>
+  </si>
+  <si>
+    <t>`0.00465, p 0.12640</t>
+  </si>
+  <si>
+    <t>`-0.00432, p 0.67037</t>
+  </si>
+  <si>
+    <t>`0.00151, p 0.57668</t>
+  </si>
+  <si>
+    <t>`-0.00056, p 0.88638</t>
+  </si>
+  <si>
+    <t>`-0.00636, p 0.39110</t>
+  </si>
+  <si>
+    <t>`0.00725, p 0.62290</t>
+  </si>
+  <si>
+    <t>`0.05499, p 0.32263</t>
+  </si>
+  <si>
+    <t>`0.18737, p 0.05020</t>
+  </si>
+  <si>
+    <t>`0.00296, p 0.70722</t>
+  </si>
+  <si>
+    <t>`0.01322, p 0.43482</t>
+  </si>
+  <si>
+    <t>`-0.03407, p 0.52627</t>
+  </si>
+  <si>
+    <t>`-0.01209, p 0.04847</t>
+  </si>
+  <si>
+    <t>`-0.02775, p 0.00276</t>
+  </si>
+  <si>
+    <t>`-0.04320, p 0.37054</t>
   </si>
 </sst>
 </file>
@@ -181,37 +244,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -221,6 +263,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -237,6 +288,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,7 +616,7 @@
   <cols>
     <col min="1" max="1" width="15.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="2" customWidth="1"/>
-    <col min="3" max="7" width="20" style="3" customWidth="1"/>
+    <col min="3" max="7" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -571,19 +626,19 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -591,164 +646,250 @@
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="4">
         <v>0.72699999999999998</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="D2" s="4">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.93</v>
+      </c>
+      <c r="G2" s="4">
+        <v>7.5999999999999998E-2</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6">
+      <c r="B3" s="8"/>
+      <c r="C3" s="2">
         <v>0.28799999999999998</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="D3" s="1">
+        <v>4.7E-2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.496</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9">
+      <c r="B7" s="9"/>
+      <c r="C7" s="3">
         <v>0.78700000000000003</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="D7" s="3">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.85299999999999998</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="3">
+      <c r="C8" s="4"/>
+      <c r="D8" s="2">
         <v>0.60499999999999998</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="E8" s="2">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.21199999999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
+      <c r="B9" s="8"/>
       <c r="D9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="E9" s="1">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
+      <c r="B10" s="8"/>
       <c r="D10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="E10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="3" t="s">
+      <c r="B11" s="8"/>
+      <c r="D11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="3" t="s">
+      <c r="B12" s="8"/>
+      <c r="D12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9">
+      <c r="B13" s="9"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="5">
         <v>1E-3</v>
       </c>
     </row>
@@ -756,8 +897,8 @@
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="E15" s="7">
+      <c r="B15" s="8"/>
+      <c r="E15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -765,8 +906,8 @@
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="E16" s="7" t="s">
+      <c r="B16" s="8"/>
+      <c r="E16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -774,8 +915,8 @@
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="E17" s="7" t="s">
+      <c r="B17" s="8"/>
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -783,8 +924,8 @@
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="E18" s="6" t="s">
+      <c r="B18" s="8"/>
+      <c r="E18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -792,104 +933,88 @@
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="E19" s="9">
+      <c r="B19" s="8"/>
+      <c r="E19" s="3">
         <v>1</v>
       </c>
-      <c r="F19" s="9"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="1">
         <v>2E-3</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="B21" s="8"/>
       <c r="F21" s="1">
         <v>0</v>
       </c>
-      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="3" t="s">
+      <c r="B22" s="8"/>
+      <c r="F22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
+      <c r="B23" s="8"/>
       <c r="F23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="B24" s="8"/>
       <c r="F24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
       <c r="F25" s="1">
         <v>0</v>
       </c>
-      <c r="G25" s="13"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="5">
         <v>0</v>
       </c>
     </row>
@@ -897,12 +1022,8 @@
       <c r="A27" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7">
+      <c r="B27" s="8"/>
+      <c r="G27" s="1">
         <v>0</v>
       </c>
     </row>
@@ -910,12 +1031,8 @@
       <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7" t="s">
+      <c r="B28" s="8"/>
+      <c r="G28" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -923,12 +1040,8 @@
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7" t="s">
+      <c r="B29" s="8"/>
+      <c r="G29" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -936,12 +1049,8 @@
       <c r="A30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7" t="s">
+      <c r="B30" s="8"/>
+      <c r="G30" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -949,12 +1058,12 @@
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/data-processed/summary_stats.xlsx
+++ b/data-processed/summary_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bbf9a23e224bd51a/Documents/GitHub/Chlamy_37_pops_pheno_constraint/data-processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="8_{7541FEAE-B6A3-48A6-8A9B-D64358009044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C682A379-637F-4802-8AAA-5F43A2071EB7}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="8_{7541FEAE-B6A3-48A6-8A9B-D64358009044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7403B7-E262-4CB8-8A3F-A6BAA56445A6}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FF39BB7-E2B9-45F5-8657-83F250E9A4B6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
   <si>
     <t>Gradients</t>
   </si>
@@ -77,24 +77,9 @@
     <t>PF75</t>
   </si>
   <si>
-    <t>`-0.64116, p 0.00006</t>
-  </si>
-  <si>
-    <t>`-0.49592,  p 0</t>
-  </si>
-  <si>
-    <t>`-0.38886 p 0.00005</t>
-  </si>
-  <si>
     <t>`0.08277, p 0</t>
   </si>
   <si>
-    <t>`0.10484, p 0</t>
-  </si>
-  <si>
-    <t>`0.16664, p 0</t>
-  </si>
-  <si>
     <t>`0.19994, p 0.00624</t>
   </si>
   <si>
@@ -104,15 +89,6 @@
     <t>`-0.30539, p 0.49977</t>
   </si>
   <si>
-    <t>`-0.66345, p 0.03740</t>
-  </si>
-  <si>
-    <t>`-1.51105, p 0.00153</t>
-  </si>
-  <si>
-    <t>`-1.84480, p 0.12155</t>
-  </si>
-  <si>
     <t>`-0.26952, p 0.37770</t>
   </si>
   <si>
@@ -122,33 +98,6 @@
     <t>`-1.66817, p 0.04733</t>
   </si>
   <si>
-    <t>`0.03581, p 0.05961</t>
-  </si>
-  <si>
-    <t>`0.08403, p 0.14458</t>
-  </si>
-  <si>
-    <t>`0.18766, p 0.10838</t>
-  </si>
-  <si>
-    <t>`0.00558, p 0.12478</t>
-  </si>
-  <si>
-    <t>`0.00226, p 0.51784</t>
-  </si>
-  <si>
-    <t>`-0.00530, p 0.38206</t>
-  </si>
-  <si>
-    <t>`0.00144, p 0.59239</t>
-  </si>
-  <si>
-    <t>`0.00465, p 0.12640</t>
-  </si>
-  <si>
-    <t>`-0.00432, p 0.67037</t>
-  </si>
-  <si>
     <t>`0.00151, p 0.57668</t>
   </si>
   <si>
@@ -158,15 +107,6 @@
     <t>`-0.00636, p 0.39110</t>
   </si>
   <si>
-    <t>`0.00725, p 0.62290</t>
-  </si>
-  <si>
-    <t>`0.05499, p 0.32263</t>
-  </si>
-  <si>
-    <t>`0.18737, p 0.05020</t>
-  </si>
-  <si>
     <t>`0.00296, p 0.70722</t>
   </si>
   <si>
@@ -183,6 +123,93 @@
   </si>
   <si>
     <t>`-0.04320, p 0.37054</t>
+  </si>
+  <si>
+    <t>`-0.45793, p 0.00002</t>
+  </si>
+  <si>
+    <t>`-0.51188, p 0.00001</t>
+  </si>
+  <si>
+    <t>`-0.62737, p 0.00002</t>
+  </si>
+  <si>
+    <t>`0.09881, p 0</t>
+  </si>
+  <si>
+    <t>`0.15598, p 0</t>
+  </si>
+  <si>
+    <t>`-0.66344, p 0.03017</t>
+  </si>
+  <si>
+    <t>`-1.53861, p 0.00009</t>
+  </si>
+  <si>
+    <t>`-2.26968, p 0.01299</t>
+  </si>
+  <si>
+    <t>`0.03581, p 0.05199</t>
+  </si>
+  <si>
+    <t>`0.08678, p 0.12844</t>
+  </si>
+  <si>
+    <t>` 0.18766, p 0.08182</t>
+  </si>
+  <si>
+    <t>`0.00712, p 0.00855</t>
+  </si>
+  <si>
+    <t>`0.00541, p 0.16813</t>
+  </si>
+  <si>
+    <t>`-0.00676, p 0.52123</t>
+  </si>
+  <si>
+    <t>`0.00144, p 0.59371</t>
+  </si>
+  <si>
+    <t>`-0.00110, p 0.90629</t>
+  </si>
+  <si>
+    <t>`0.00531, p 0.07877</t>
+  </si>
+  <si>
+    <t>`0.21179, p 0.06324</t>
+  </si>
+  <si>
+    <t>`04000, p 0.17423</t>
+  </si>
+  <si>
+    <t>`0.01604, p 0.26852</t>
+  </si>
+  <si>
+    <t>`0.07937, p 0.07165</t>
+  </si>
+  <si>
+    <t>`0.06436, p 0.26831</t>
+  </si>
+  <si>
+    <t>`0.30046, p 0.23676</t>
+  </si>
+  <si>
+    <t>`-0.06664, p 0.54793</t>
+  </si>
+  <si>
+    <t>`-0.03796, p 0.55821</t>
+  </si>
+  <si>
+    <t>`-0.01390, p 0.71701</t>
+  </si>
+  <si>
+    <t>`-0.02957, p 0.30642</t>
+  </si>
+  <si>
+    <t>`-0.18163, p 0.20907</t>
+  </si>
+  <si>
+    <t>`0, p 1</t>
   </si>
 </sst>
 </file>
@@ -244,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -272,6 +299,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -650,16 +680,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="4">
-        <v>0.72699999999999998</v>
+        <v>0.74</v>
       </c>
       <c r="D2" s="4">
-        <v>0.72399999999999998</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="E2" s="4">
-        <v>0.17599999999999999</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F2" s="4">
-        <v>0.93</v>
+        <v>0.84699999999999998</v>
       </c>
       <c r="G2" s="4">
         <v>7.5999999999999998E-2</v>
@@ -670,17 +700,17 @@
         <v>8</v>
       </c>
       <c r="B3" s="8"/>
-      <c r="C3" s="2">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="D3" s="1">
-        <v>4.7E-2</v>
+      <c r="C3" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0.17699999999999999</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="F3" s="2">
-        <v>0.496</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -692,19 +722,19 @@
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -713,19 +743,19 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -734,19 +764,19 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -755,16 +785,16 @@
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="3">
-        <v>0.78700000000000003</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="D7" s="3">
-        <v>0.66500000000000004</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="E7" s="3">
         <v>0.11899999999999999</v>
       </c>
       <c r="F7" s="6">
-        <v>1.2E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="G7" s="3">
         <v>0.85299999999999998</v>
@@ -782,7 +812,7 @@
         <v>0.60499999999999998</v>
       </c>
       <c r="E8" s="2">
-        <v>0.71599999999999997</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="F8" s="4">
         <v>0.35</v>
@@ -800,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>4.3999999999999997E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -815,16 +845,16 @@
       </c>
       <c r="B10" s="8"/>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -833,16 +863,16 @@
       </c>
       <c r="B11" s="8"/>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -851,16 +881,16 @@
       </c>
       <c r="B12" s="8"/>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -890,7 +920,13 @@
         <v>4</v>
       </c>
       <c r="E14" s="5">
-        <v>1E-3</v>
+        <v>2E-3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.36</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,6 +937,12 @@
       <c r="E15" s="1">
         <v>0</v>
       </c>
+      <c r="F15" s="2">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -908,7 +950,13 @@
       </c>
       <c r="B16" s="8"/>
       <c r="E16" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -917,7 +965,13 @@
       </c>
       <c r="B17" s="8"/>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -925,8 +979,14 @@
         <v>11</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="E18" s="2" t="s">
-        <v>24</v>
+      <c r="E18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -937,7 +997,12 @@
       <c r="E19" s="3">
         <v>1</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
@@ -952,7 +1017,9 @@
       <c r="F20" s="1">
         <v>2E-3</v>
       </c>
-      <c r="G20" s="4"/>
+      <c r="G20" s="4">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -962,6 +1029,9 @@
       <c r="F21" s="1">
         <v>0</v>
       </c>
+      <c r="G21" s="2">
+        <v>0.14299999999999999</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -969,7 +1039,10 @@
       </c>
       <c r="B22" s="8"/>
       <c r="F22" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -978,7 +1051,10 @@
       </c>
       <c r="B23" s="8"/>
       <c r="F23" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -987,7 +1063,10 @@
       </c>
       <c r="B24" s="8"/>
       <c r="F24" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1001,7 +1080,9 @@
       <c r="F25" s="1">
         <v>0</v>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
@@ -1033,7 +1114,7 @@
       </c>
       <c r="B28" s="8"/>
       <c r="G28" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1042,7 +1123,7 @@
       </c>
       <c r="B29" s="8"/>
       <c r="G29" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1051,7 +1132,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="G30" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
